--- a/resources/templates/standard/B2100-02.xlsx
+++ b/resources/templates/standard/B2100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>시정 및 예방조치 등록대장</t>
   </si>
@@ -546,12 +549,14 @@
   <sheetFormatPr defaultRowHeight="17" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="2.58203125" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -696,30 +701,30 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
@@ -734,31 +739,31 @@
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
       <c r="AN4" s="4"/>
       <c r="AO4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="4"/>
       <c r="AS4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
@@ -771,20 +776,20 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -860,7 +865,7 @@
       <c r="AM6" s="8"/>
       <c r="AN6" s="8"/>
       <c r="AO6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP6" s="4"/>
       <c r="AQ6" s="8"/>
@@ -911,7 +916,7 @@
       <c r="AM7" s="8"/>
       <c r="AN7" s="8"/>
       <c r="AO7" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" s="9"/>
       <c r="AQ7" s="10"/>
@@ -962,7 +967,7 @@
       <c r="AM8" s="8"/>
       <c r="AN8" s="8"/>
       <c r="AO8" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8" s="9"/>
       <c r="AQ8" s="10"/>
@@ -1013,7 +1018,7 @@
       <c r="AM9" s="8"/>
       <c r="AN9" s="8"/>
       <c r="AO9" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP9" s="9"/>
       <c r="AQ9" s="10"/>
@@ -1064,7 +1069,7 @@
       <c r="AM10" s="10"/>
       <c r="AN10" s="10"/>
       <c r="AO10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP10" s="9"/>
       <c r="AQ10" s="10"/>
@@ -1115,7 +1120,7 @@
       <c r="AM11" s="10"/>
       <c r="AN11" s="10"/>
       <c r="AO11" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP11" s="9"/>
       <c r="AQ11" s="10"/>
@@ -1166,7 +1171,7 @@
       <c r="AM12" s="10"/>
       <c r="AN12" s="10"/>
       <c r="AO12" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP12" s="9"/>
       <c r="AQ12" s="10"/>
@@ -1217,7 +1222,7 @@
       <c r="AM13" s="10"/>
       <c r="AN13" s="10"/>
       <c r="AO13" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP13" s="9"/>
       <c r="AQ13" s="10"/>
@@ -1268,7 +1273,7 @@
       <c r="AM14" s="10"/>
       <c r="AN14" s="10"/>
       <c r="AO14" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP14" s="9"/>
       <c r="AQ14" s="10"/>
@@ -1319,7 +1324,7 @@
       <c r="AM15" s="10"/>
       <c r="AN15" s="10"/>
       <c r="AO15" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" s="9"/>
       <c r="AQ15" s="10"/>
@@ -1370,7 +1375,7 @@
       <c r="AM16" s="10"/>
       <c r="AN16" s="10"/>
       <c r="AO16" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP16" s="9"/>
       <c r="AQ16" s="10"/>
@@ -1421,7 +1426,7 @@
       <c r="AM17" s="10"/>
       <c r="AN17" s="10"/>
       <c r="AO17" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP17" s="9"/>
       <c r="AQ17" s="10"/>
@@ -1472,7 +1477,7 @@
       <c r="AM18" s="10"/>
       <c r="AN18" s="10"/>
       <c r="AO18" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP18" s="9"/>
       <c r="AQ18" s="10"/>
@@ -1523,7 +1528,7 @@
       <c r="AM19" s="10"/>
       <c r="AN19" s="10"/>
       <c r="AO19" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP19" s="9"/>
       <c r="AQ19" s="10"/>
@@ -1574,7 +1579,7 @@
       <c r="AM20" s="10"/>
       <c r="AN20" s="10"/>
       <c r="AO20" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP20" s="9"/>
       <c r="AQ20" s="10"/>
@@ -1625,7 +1630,7 @@
       <c r="AM21" s="10"/>
       <c r="AN21" s="10"/>
       <c r="AO21" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP21" s="9"/>
       <c r="AQ21" s="10"/>
@@ -1676,7 +1681,7 @@
       <c r="AM22" s="10"/>
       <c r="AN22" s="10"/>
       <c r="AO22" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP22" s="9"/>
       <c r="AQ22" s="10"/>
@@ -1727,7 +1732,7 @@
       <c r="AM23" s="10"/>
       <c r="AN23" s="10"/>
       <c r="AO23" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" s="9"/>
       <c r="AQ23" s="10"/>
@@ -1778,7 +1783,7 @@
       <c r="AM24" s="10"/>
       <c r="AN24" s="10"/>
       <c r="AO24" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP24" s="9"/>
       <c r="AQ24" s="10"/>
@@ -1829,7 +1834,7 @@
       <c r="AM25" s="10"/>
       <c r="AN25" s="10"/>
       <c r="AO25" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP25" s="7"/>
       <c r="AQ25" s="12"/>
